--- a/Magic_stocks_read_file.xlsx
+++ b/Magic_stocks_read_file.xlsx
@@ -5,20 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Magic_Stocks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCE55D3-CB4A-4982-8A8D-6503C2A53B2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03B0839-9925-41E3-B57F-7EEB87C2CB79}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3722F58C-EB81-4D02-B60E-D8F800BE24A1}"/>
+    <workbookView xWindow="2850" yWindow="2850" windowWidth="21600" windowHeight="11385" xr2:uid="{3722F58C-EB81-4D02-B60E-D8F800BE24A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Python" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -179,8 +176,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -451,38 +448,38 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="3" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="2" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="2" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="5" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="5" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="5" xfId="5" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="6" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="5" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="5" xfId="6" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="6" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="7" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="7" xfId="6" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="3" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="3" xfId="5" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="7" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="4" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="4" applyFont="1" applyBorder="1"/>
@@ -493,19 +490,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="20 % - Dekorfärg4" xfId="4" builtinId="42"/>
@@ -519,7 +516,7 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
@@ -813,6 +810,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
@@ -820,15 +826,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
@@ -944,6 +941,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3850-4756-B61A-430B5495A0A5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -959,6 +961,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-3850-4756-B61A-430B5495A0A5}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -1158,6 +1165,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2062-4EAF-B4FE-2C6E1DD05159}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1173,6 +1185,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2062-4EAF-B4FE-2C6E1DD05159}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2496,168 +2513,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Overview"/>
-      <sheetName val="Python"/>
-      <sheetName val="Python2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O2">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O3">
-            <v>164.89999999999998</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O4">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O6">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O12">
-            <v>77</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O17">
-            <v>68</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O18">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="O19">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3168,7 +3023,7 @@
 <richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <dxfs count="7">
     <x:dxf>
-      <x:numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
+      <x:numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -3180,7 +3035,7 @@
       <x:numFmt numFmtId="14" formatCode="0.00%"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="165" formatCode="_-* #,##0\ [$kr-41D]_-;\-* #,##0\ [$kr-41D]_-;_-* &quot;-&quot;\ [$kr-41D]_-;_-@_-"/>
+      <x:numFmt numFmtId="164" formatCode="_-* #,##0\ [$kr-41D]_-;\-* #,##0\ [$kr-41D]_-;_-* &quot;-&quot;\ [$kr-41D]_-;_-@_-"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="27" formatCode="yyyy/mm/dd\ hh:mm"/>
@@ -3216,7 +3071,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31752BBB-B173-4CC0-9F09-547BEDF2D3D8}" name="Tabell1" displayName="Tabell1" ref="A1:P20" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18" totalsRowBorderDxfId="16" headerRowCellStyle="Neutral" dataCellStyle="60 % - Dekorfärg3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31752BBB-B173-4CC0-9F09-547BEDF2D3D8}" name="Tabell1" displayName="Tabell1" ref="A1:P20" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16" headerRowCellStyle="Neutral" dataCellStyle="60 % - Dekorfärg3">
   <autoFilter ref="A1:P20" xr:uid="{12A8F980-6EA7-4DF9-BCDC-E895312D6D3C}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{CAD8539A-96CC-4FCA-84F2-A98A73D4B2CE}" name="Stock name               Devidend per stock" dataDxfId="15" dataCellStyle="60 % - Dekorfärg3"/>
@@ -3634,7 +3489,7 @@
         <v>1000</v>
       </c>
       <c r="O2" s="3">
-        <f t="shared" ref="O2:O9" si="0">SUM(B2:M2)*N2</f>
+        <f t="shared" ref="O2:O3" si="0">SUM(B2:M2)*N2</f>
         <v>1500</v>
       </c>
       <c r="P2" s="4" cm="1">
